--- a/Conf_app/App_py/Base - Respon.xlsx
+++ b/Conf_app/App_py/Base - Respon.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kvlopes\Desktop\Scripts\Auto-Ficha-OPE\Conf_app\App_py\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kvlopes\Desktop\Scripts\Hxg_auto\Conf_app\App_py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07944C60-134A-444A-8801-E354D4E127DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331C8318-EB8B-49DE-99DC-4ACF192F5E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cont. Maquinas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$47</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento__código">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_MÊS">#N/A</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
   <si>
     <t>RESPONSAVEL</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>COPERTRAN</t>
-  </si>
-  <si>
-    <t>FERNANDO BREGUEDO</t>
   </si>
   <si>
     <t>VOLVO - L60F</t>
@@ -193,7 +190,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,13 +222,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -247,14 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -281,24 +264,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -617,7 +597,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.44140625" style="5" bestFit="1" customWidth="1"/>
@@ -650,7 +630,7 @@
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2">
         <v>15049</v>
@@ -670,7 +650,7 @@
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2">
         <v>15054</v>
@@ -690,7 +670,7 @@
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
         <v>15033</v>
@@ -699,24 +679,24 @@
         <v>2094170</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>15276</v>
+        <v>15307</v>
       </c>
       <c r="C5" s="2">
-        <v>2094173</v>
+        <v>2094174</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -725,18 +705,18 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>15307</v>
+        <v>24811</v>
       </c>
       <c r="C6" s="2">
-        <v>2094174</v>
+        <v>2094179</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -745,78 +725,78 @@
         <v>8</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>15047</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2094430</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="2">
-        <v>24811</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2094179</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>15047</v>
+        <v>15035</v>
       </c>
       <c r="C8" s="2">
-        <v>2094430</v>
+        <v>2094476</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
-        <v>15035</v>
+        <v>15031</v>
       </c>
       <c r="C9" s="2">
-        <v>2094476</v>
+        <v>2094535</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2">
-        <v>15031</v>
+        <v>15277</v>
       </c>
       <c r="C10" s="2">
-        <v>2094535</v>
+        <v>2095036</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -825,387 +805,387 @@
         <v>8</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>15277</v>
+        <v>24805</v>
       </c>
       <c r="C11" s="2">
-        <v>2095036</v>
+        <v>2095064</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>24803</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2095065</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B12" s="2">
-        <v>24805</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2095064</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>24803</v>
+        <v>15313</v>
       </c>
       <c r="C13" s="2">
-        <v>2095065</v>
+        <v>2095162</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>15313</v>
+        <v>15285</v>
       </c>
       <c r="C14" s="2">
-        <v>2095162</v>
+        <v>2095199</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>15285</v>
+        <v>15312</v>
       </c>
       <c r="C15" s="2">
-        <v>2095199</v>
+        <v>2095253</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>15312</v>
+        <v>15036</v>
       </c>
       <c r="C16" s="2">
-        <v>2095253</v>
+        <v>2095254</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>15036</v>
+        <v>15275</v>
       </c>
       <c r="C17" s="2">
-        <v>2095254</v>
+        <v>2095268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
-        <v>15275</v>
+        <v>15274</v>
       </c>
       <c r="C18" s="2">
-        <v>2095268</v>
+        <v>2095314</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2">
-        <v>15274</v>
+        <v>15269</v>
       </c>
       <c r="C19" s="2">
-        <v>2095314</v>
+        <v>2095324</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>15269</v>
+        <v>15057</v>
       </c>
       <c r="C20" s="2">
-        <v>2095324</v>
+        <v>2095374</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2">
-        <v>15057</v>
+        <v>15039</v>
       </c>
       <c r="C21" s="2">
-        <v>2095374</v>
+        <v>2095489</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B22" s="2">
-        <v>15039</v>
+        <v>24807</v>
       </c>
       <c r="C22" s="2">
-        <v>2095489</v>
+        <v>2095927</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>24807</v>
+        <v>24806</v>
       </c>
       <c r="C23" s="2">
-        <v>2095927</v>
+        <v>2096228</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2">
-        <v>15270</v>
+        <v>15030</v>
       </c>
       <c r="C24" s="2">
-        <v>2096003</v>
+        <v>2096424</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2">
-        <v>24806</v>
+        <v>15037</v>
       </c>
       <c r="C25" s="2">
-        <v>2096228</v>
+        <v>2096569</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2">
-        <v>15030</v>
+        <v>11002</v>
       </c>
       <c r="C26" s="2">
-        <v>2096424</v>
+        <v>2096570</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B27" s="2">
-        <v>15037</v>
+        <v>15044</v>
       </c>
       <c r="C27" s="2">
-        <v>2096569</v>
+        <v>2096626</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2">
-        <v>11002</v>
+        <v>15053</v>
       </c>
       <c r="C28" s="2">
-        <v>2096570</v>
+        <v>2096633</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2">
+        <v>24809</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2096842</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B29" s="2">
-        <v>15044</v>
-      </c>
-      <c r="C29" s="2">
-        <v>2096626</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1213,456 +1193,369 @@
         <v>6</v>
       </c>
       <c r="B30" s="2">
-        <v>15268</v>
+        <v>11006</v>
       </c>
       <c r="C30" s="2">
-        <v>2096633</v>
+        <v>2096882</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2">
-        <v>24809</v>
+        <v>15310</v>
       </c>
       <c r="C31" s="2">
-        <v>2096842</v>
+        <v>2096953</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2">
-        <v>11006</v>
+        <v>15055</v>
       </c>
       <c r="C32" s="2">
-        <v>2096882</v>
+        <v>2096973</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B33" s="2">
-        <v>15056</v>
+        <v>24335</v>
       </c>
       <c r="C33" s="2">
-        <v>2096915</v>
+        <v>2096977</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B34" s="2">
-        <v>15310</v>
+        <v>15314</v>
       </c>
       <c r="C34" s="2">
-        <v>2096953</v>
+        <v>2098176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2">
+        <v>15278</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2098270</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="2">
-        <v>15055</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2096973</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2">
-        <v>24335</v>
+        <v>15272</v>
       </c>
       <c r="C36" s="2">
-        <v>2096977</v>
+        <v>2098516</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B37" s="2">
-        <v>15314</v>
+        <v>15270</v>
       </c>
       <c r="C37" s="2">
-        <v>2098176</v>
+        <v>2098751</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B38" s="2">
-        <v>15278</v>
+        <v>15032</v>
       </c>
       <c r="C38" s="2">
-        <v>2098270</v>
+        <v>2098755</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2">
-        <v>15272</v>
+        <v>15038</v>
       </c>
       <c r="C39" s="2">
-        <v>2098516</v>
+        <v>2099635</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B40" s="2">
-        <v>15270</v>
+        <v>15050</v>
       </c>
       <c r="C40" s="2">
-        <v>2098751</v>
+        <v>2099932</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B41" s="2">
-        <v>15032</v>
+        <v>24804</v>
       </c>
       <c r="C41" s="2">
-        <v>2098755</v>
+        <v>20924188</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B42" s="2">
-        <v>15038</v>
+        <v>15040</v>
       </c>
       <c r="C42" s="2">
-        <v>2099635</v>
+        <v>20924192</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B43" s="2">
-        <v>15050</v>
+        <v>15284</v>
       </c>
       <c r="C43" s="2">
-        <v>2099932</v>
+        <v>20924216</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2">
-        <v>24804</v>
+        <v>15279</v>
       </c>
       <c r="C44" s="2">
-        <v>20924188</v>
+        <v>20924217</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>15040</v>
+        <v>15268</v>
       </c>
       <c r="C45" s="2">
-        <v>20924192</v>
+        <v>20924343</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2">
-        <v>15284</v>
+        <v>15059</v>
       </c>
       <c r="C46" s="2">
-        <v>20924216</v>
+        <v>20925055</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B47" s="2">
-        <v>15279</v>
+        <v>15056</v>
       </c>
       <c r="C47" s="2">
-        <v>20924217</v>
+        <v>20925255</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="2">
-        <v>15268</v>
-      </c>
-      <c r="C48" s="2">
-        <v>20924343</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="2">
-        <v>15059</v>
-      </c>
-      <c r="C49" s="2">
-        <v>20925055</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="6"/>
-    </row>
-    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E59" s="6"/>
-    </row>
-    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E60" s="6"/>
-    </row>
-    <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E61" s="6"/>
-    </row>
-    <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E62" s="6"/>
-    </row>
-    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E63" s="6"/>
-    </row>
-    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E64" s="6"/>
-    </row>
-    <row r="65" spans="5:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E65" s="6"/>
-    </row>
-    <row r="66" spans="5:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E66" s="6"/>
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F66" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="B1 B50:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <autoFilter ref="A1:F47" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F47">
+      <sortCondition ref="C1:C47"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B48:B1048576 B1">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Conf_app/App_py/Base - Respon.xlsx
+++ b/Conf_app/App_py/Base - Respon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kvlopes\Desktop\Scripts\Hxg_auto\Conf_app\App_py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331C8318-EB8B-49DE-99DC-4ACF192F5E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A6C4DB-263B-4291-BBBF-E819780E9CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Cont. Maquinas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$45</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento__código">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_MÊS">#N/A</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="46">
   <si>
     <t>RESPONSAVEL</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CASE 721-E</t>
   </si>
   <si>
     <t>BECEGATO</t>
@@ -597,7 +594,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.44140625" style="5" bestFit="1" customWidth="1"/>
@@ -650,7 +647,7 @@
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2">
         <v>15054</v>
@@ -670,7 +667,7 @@
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2">
         <v>15033</v>
@@ -690,13 +687,13 @@
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>15307</v>
+        <v>24811</v>
       </c>
       <c r="C5" s="2">
-        <v>2094174</v>
+        <v>2094179</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -705,21 +702,21 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>24811</v>
+        <v>15047</v>
       </c>
       <c r="C6" s="2">
-        <v>2094179</v>
+        <v>2094430</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>8</v>
@@ -730,53 +727,53 @@
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2">
-        <v>15047</v>
+        <v>15035</v>
       </c>
       <c r="C7" s="2">
-        <v>2094430</v>
+        <v>2094476</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2">
-        <v>15035</v>
+        <v>15031</v>
       </c>
       <c r="C8" s="2">
-        <v>2094476</v>
+        <v>2094535</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2">
-        <v>15031</v>
+        <v>15277</v>
       </c>
       <c r="C9" s="2">
-        <v>2094535</v>
+        <v>2095036</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -785,27 +782,27 @@
         <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>15277</v>
+        <v>24805</v>
       </c>
       <c r="C10" s="2">
-        <v>2095036</v>
+        <v>2095064</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -813,10 +810,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>24805</v>
+        <v>24803</v>
       </c>
       <c r="C11" s="2">
-        <v>2095064</v>
+        <v>2095065</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>23</v>
@@ -830,22 +827,22 @@
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>24803</v>
+        <v>15313</v>
       </c>
       <c r="C12" s="2">
-        <v>2095065</v>
+        <v>2095162</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -853,19 +850,19 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>15313</v>
+        <v>15285</v>
       </c>
       <c r="C13" s="2">
-        <v>2095162</v>
+        <v>2095199</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -873,19 +870,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>15285</v>
+        <v>15312</v>
       </c>
       <c r="C14" s="2">
-        <v>2095199</v>
+        <v>2095253</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -893,10 +890,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>15312</v>
+        <v>15036</v>
       </c>
       <c r="C15" s="2">
-        <v>2095253</v>
+        <v>2095254</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
@@ -913,19 +910,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>15036</v>
+        <v>15275</v>
       </c>
       <c r="C16" s="2">
-        <v>2095254</v>
+        <v>2095268</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -933,119 +930,119 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>15275</v>
+        <v>15274</v>
       </c>
       <c r="C17" s="2">
-        <v>2095268</v>
+        <v>2095314</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>15274</v>
+        <v>15269</v>
       </c>
       <c r="C18" s="2">
-        <v>2095314</v>
+        <v>2095324</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2">
-        <v>15269</v>
+        <v>15057</v>
       </c>
       <c r="C19" s="2">
-        <v>2095324</v>
+        <v>2095374</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2">
-        <v>15057</v>
+        <v>15039</v>
       </c>
       <c r="C20" s="2">
-        <v>2095374</v>
+        <v>2095489</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2">
-        <v>15039</v>
+        <v>24807</v>
       </c>
       <c r="C21" s="2">
-        <v>2095489</v>
+        <v>2095927</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2">
-        <v>24807</v>
+        <v>15278</v>
       </c>
       <c r="C22" s="2">
-        <v>2095927</v>
+        <v>2096028</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1190,7 +1187,7 @@
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2">
         <v>11006</v>
@@ -1210,7 +1207,7 @@
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="2">
         <v>15310</v>
@@ -1250,7 +1247,7 @@
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B33" s="2">
         <v>24335</v>
@@ -1290,53 +1287,53 @@
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B35" s="2">
-        <v>15278</v>
+        <v>15272</v>
       </c>
       <c r="C35" s="2">
-        <v>2098270</v>
+        <v>2098516</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B36" s="2">
-        <v>15272</v>
+        <v>15270</v>
       </c>
       <c r="C36" s="2">
-        <v>2098516</v>
+        <v>2098751</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>15270</v>
+        <v>15032</v>
       </c>
       <c r="C37" s="2">
-        <v>2098751</v>
+        <v>2098755</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>40</v>
@@ -1345,27 +1342,27 @@
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B38" s="2">
-        <v>15032</v>
+        <v>15038</v>
       </c>
       <c r="C38" s="2">
-        <v>2098755</v>
+        <v>2099635</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1373,110 +1370,110 @@
         <v>19</v>
       </c>
       <c r="B39" s="2">
-        <v>15038</v>
+        <v>15050</v>
       </c>
       <c r="C39" s="2">
-        <v>2099635</v>
+        <v>2099932</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B40" s="2">
-        <v>15050</v>
+        <v>24804</v>
       </c>
       <c r="C40" s="2">
-        <v>2099932</v>
+        <v>20924188</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B41" s="2">
-        <v>24804</v>
+        <v>15284</v>
       </c>
       <c r="C41" s="2">
-        <v>20924188</v>
+        <v>20924216</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2">
-        <v>15040</v>
+        <v>15279</v>
       </c>
       <c r="C42" s="2">
-        <v>20924192</v>
+        <v>20924217</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>15284</v>
+        <v>15268</v>
       </c>
       <c r="C43" s="2">
-        <v>20924216</v>
+        <v>20924343</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B44" s="2">
-        <v>15279</v>
+        <v>15059</v>
       </c>
       <c r="C44" s="2">
-        <v>20924217</v>
+        <v>20925055</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
@@ -1485,76 +1482,36 @@
         <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B45" s="2">
-        <v>15268</v>
+        <v>15056</v>
       </c>
       <c r="C45" s="2">
-        <v>20924343</v>
+        <v>20925255</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="2">
-        <v>15059</v>
-      </c>
-      <c r="C46" s="2">
-        <v>20925055</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="2">
-        <v>15056</v>
-      </c>
-      <c r="C47" s="2">
-        <v>20925255</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F47" s="3" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F47">
-      <sortCondition ref="C1:C47"/>
+  <autoFilter ref="A1:F45" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F45">
+      <sortCondition ref="C1:C45"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B48:B1048576 B1">
+  <conditionalFormatting sqref="B46:B1048576 B1">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Conf_app/App_py/Base - Respon.xlsx
+++ b/Conf_app/App_py/Base - Respon.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kvlopes\Desktop\Scripts\Hxg_auto\Conf_app\App_py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A6C4DB-263B-4291-BBBF-E819780E9CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BFF851-26A1-43D3-ADF6-9117070A0C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cont. Maquinas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cont. Maquinas'!$A$1:$F$44</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento__código">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_MÊS">#N/A</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="45">
   <si>
     <t>RESPONSAVEL</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>CASE - 621D</t>
-  </si>
-  <si>
-    <t>CLAUDIO CESAR CABRIOTTI</t>
   </si>
   <si>
     <t>ET7 MÁQUINAS</t>
@@ -647,7 +644,7 @@
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2">
         <v>15054</v>
@@ -667,7 +664,7 @@
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2">
         <v>15033</v>
@@ -747,33 +744,33 @@
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>15031</v>
+        <v>24804</v>
       </c>
       <c r="C8" s="2">
-        <v>2094535</v>
+        <v>2094481</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
-        <v>15277</v>
+        <v>15031</v>
       </c>
       <c r="C9" s="2">
-        <v>2095036</v>
+        <v>2094535</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -782,27 +779,27 @@
         <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2">
-        <v>24805</v>
+        <v>15277</v>
       </c>
       <c r="C10" s="2">
-        <v>2095064</v>
+        <v>2095036</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -810,10 +807,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>24803</v>
+        <v>24805</v>
       </c>
       <c r="C11" s="2">
-        <v>2095065</v>
+        <v>2095064</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>23</v>
@@ -827,22 +824,22 @@
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>15313</v>
+        <v>24803</v>
       </c>
       <c r="C12" s="2">
-        <v>2095162</v>
+        <v>2095065</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -850,19 +847,19 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>15285</v>
+        <v>15313</v>
       </c>
       <c r="C13" s="2">
-        <v>2095199</v>
+        <v>2095162</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -870,19 +867,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>15312</v>
+        <v>15285</v>
       </c>
       <c r="C14" s="2">
-        <v>2095253</v>
+        <v>2095199</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -890,10 +887,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>15036</v>
+        <v>15312</v>
       </c>
       <c r="C15" s="2">
-        <v>2095254</v>
+        <v>2095253</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
@@ -910,19 +907,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>15275</v>
+        <v>15036</v>
       </c>
       <c r="C16" s="2">
-        <v>2095268</v>
+        <v>2095254</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -930,64 +927,64 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>15274</v>
+        <v>15275</v>
       </c>
       <c r="C17" s="2">
-        <v>2095314</v>
+        <v>2095268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
-        <v>15269</v>
+        <v>15274</v>
       </c>
       <c r="C18" s="2">
-        <v>2095324</v>
+        <v>2095314</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2">
-        <v>15057</v>
+        <v>15269</v>
       </c>
       <c r="C19" s="2">
-        <v>2095374</v>
+        <v>2095324</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2">
         <v>15039</v>
@@ -1022,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1207,7 +1204,7 @@
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="2">
         <v>15310</v>
@@ -1382,38 +1379,38 @@
         <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B40" s="2">
-        <v>24804</v>
+        <v>15284</v>
       </c>
       <c r="C40" s="2">
-        <v>20924188</v>
+        <v>20924216</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B41" s="2">
-        <v>15284</v>
+        <v>15279</v>
       </c>
       <c r="C41" s="2">
-        <v>20924216</v>
+        <v>20924217</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
@@ -1422,70 +1419,70 @@
         <v>8</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>15279</v>
+        <v>15268</v>
       </c>
       <c r="C42" s="2">
-        <v>20924217</v>
+        <v>20924343</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B43" s="2">
-        <v>15268</v>
+        <v>15059</v>
       </c>
       <c r="C43" s="2">
-        <v>20924343</v>
+        <v>20925055</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B44" s="2">
-        <v>15059</v>
+        <v>15057</v>
       </c>
       <c r="C44" s="2">
-        <v>20925055</v>
+        <v>20925101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>19</v>
       </c>
@@ -1506,9 +1503,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F45" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F45">
-      <sortCondition ref="C1:C45"/>
+  <autoFilter ref="A1:F44" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F44">
+      <sortCondition ref="C1:C44"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B46:B1048576 B1">

--- a/Conf_app/App_py/Base - Respon.xlsx
+++ b/Conf_app/App_py/Base - Respon.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kvlopes\Desktop\Scripts\Hxg_auto\Conf_app\App_py\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97EF14CD-5FEE-4B47-92B6-8F3B5F0818EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Cont. Maquinas"/>
+    <sheet name="Cont. Maquinas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">='Cont. Maquinas'!$A$1:$F$44</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Equipamento__código">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_MÊS">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Mês1">#N/A</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="45">
   <si>
     <t>RESPONSAVEL</t>
   </si>
@@ -161,8 +167,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,14 +179,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF7f7f7f"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -195,7 +200,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF43948c"/>
+        <fgColor rgb="FF43948C"/>
       </patternFill>
     </fill>
   </fills>
@@ -209,16 +214,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7f7f7f"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7f7f7f"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7f7f7f"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7f7f7f"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -227,34 +232,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -265,10 +273,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -306,71 +314,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -398,7 +406,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -421,11 +429,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -434,13 +442,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -450,7 +458,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -459,7 +467,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -468,7 +476,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -476,10 +484,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -544,29 +552,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="5" width="40.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="23.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="17.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="24.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="40.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -579,883 +587,863 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>15049</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2000417</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>15054</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>2094146</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>15033</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>2094170</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>24811</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>2094179</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>15047</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>2094430</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>15035</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>2094476</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>24804</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>2094481</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>15031</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>2094535</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>15277</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>2095036</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>24805</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>2095064</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>24803</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>2095065</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>15313</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>2095162</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>15285</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>2095199</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>15312</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>2095253</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>15036</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>2095254</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>15275</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>2095268</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>15274</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>2095314</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>15269</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>2095324</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>15039</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>2095489</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>24807</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>2095927</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>15278</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>2096028</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>24806</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>2096228</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>15030</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>2096424</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>15037</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>2096569</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>11002</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>2096570</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="5">
         <v>15044</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>2096626</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="5">
         <v>15053</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>2096633</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>24809</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>2096842</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>11006</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>2096882</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>15310</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>2096953</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>15055</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>2096973</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>24335</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <v>2096977</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="E33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>15314</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <v>2098176</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>15272</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>2098516</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="E35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>15270</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>2098751</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>15032</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="5">
         <v>2098755</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="E37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="4">
-        <v>15038</v>
-      </c>
-      <c r="C38" s="4">
-        <v>2099635</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="B38" s="5">
+        <v>15050</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2099932</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="5">
+        <v>15284</v>
+      </c>
+      <c r="C39" s="5">
+        <v>20924216</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="5">
+        <v>15279</v>
+      </c>
+      <c r="C40" s="5">
+        <v>20924217</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="3" t="s">
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="5">
+        <v>15268</v>
+      </c>
+      <c r="C41" s="5">
+        <v>20924343</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="5">
+        <v>15059</v>
+      </c>
+      <c r="C42" s="5">
+        <v>20925055</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="4">
-        <v>15050</v>
-      </c>
-      <c r="C39" s="4">
-        <v>2099932</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" s="4">
-        <v>15284</v>
-      </c>
-      <c r="C40" s="4">
-        <v>20924216</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="3" t="s">
+      <c r="B43" s="5">
+        <v>15057</v>
+      </c>
+      <c r="C43" s="5">
+        <v>20925101</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="4">
-        <v>15279</v>
-      </c>
-      <c r="C41" s="4">
-        <v>20924217</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="4">
-        <v>15268</v>
-      </c>
-      <c r="C42" s="4">
-        <v>20924343</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="4">
-        <v>15059</v>
-      </c>
-      <c r="C43" s="4">
-        <v>20925055</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="4">
-        <v>15057</v>
-      </c>
-      <c r="C44" s="4">
-        <v>20925101</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" s="4">
+      <c r="B44" s="5">
         <v>15056</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C44" s="5">
         <v>20925255</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="E44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>12</v>
       </c>
     </row>
